--- a/exports/POLYCAB_full_report.xlsx
+++ b/exports/POLYCAB_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:U67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>4.36</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44581.55208333334</v>
+        <v>44582.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>2669</v>
+        <v>2542.05</v>
       </c>
       <c r="I2" t="n">
         <v>2571.43157818942</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>7.27</v>
+        <v>2.16</v>
       </c>
       <c r="L2" t="n">
         <v>0.95</v>
       </c>
       <c r="M2" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="N2" t="n">
-        <v>2.06</v>
+        <v>5.96</v>
       </c>
       <c r="O2" t="n">
         <v>2.5</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>11.04</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44635.38541666666</v>
+        <v>44635.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>2338.35</v>
+        <v>2397</v>
       </c>
       <c r="I3" t="n">
         <v>2374.385476060785</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>53</v>
+        <v>53.16666666666666</v>
       </c>
       <c r="K3" t="n">
-        <v>8.01</v>
+        <v>5.71</v>
       </c>
       <c r="L3" t="n">
         <v>6.1</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8.42</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44673.38541666666</v>
+        <v>44673.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>2768.1</v>
+        <v>2534</v>
       </c>
       <c r="I4" t="n">
         <v>2570.368713733316</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>37.83333333333334</v>
+        <v>38</v>
       </c>
       <c r="K4" t="n">
-        <v>15.48</v>
+        <v>5.72</v>
       </c>
       <c r="L4" t="n">
         <v>3.22</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>14.56</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44736.55208333334</v>
+        <v>44739.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>2216.4</v>
+        <v>2279.1</v>
       </c>
       <c r="I5" t="n">
         <v>2265.568136028096</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>63</v>
+        <v>65.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>12.53</v>
+        <v>10.06</v>
       </c>
       <c r="L5" t="n">
         <v>9.390000000000001</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44756.55208333334</v>
+        <v>44757.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>2142.55</v>
+        <v>2123.9</v>
       </c>
       <c r="I6" t="n">
         <v>2129.772620802461</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.99</v>
+        <v>-6.81</v>
       </c>
       <c r="L6" t="n">
-        <v>6.39</v>
+        <v>7.68</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>6.34</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44769.55208333334</v>
+        <v>44770.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>2221</v>
+        <v>2281.95</v>
       </c>
       <c r="I7" t="n">
         <v>2258.524110715307</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.57</v>
+        <v>-7.44</v>
       </c>
       <c r="L7" t="n">
-        <v>7.82</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M7" t="n">
         <v>1.96</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.12</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44795.38541666666</v>
+        <v>44795.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>2361</v>
+        <v>2349.8</v>
       </c>
       <c r="I8" t="n">
         <v>2359.598429938152</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>3.46</v>
+        <v>2.97</v>
       </c>
       <c r="L8" t="n">
         <v>2.27</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>4.87</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44803.38541666666</v>
+        <v>44803.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>2450</v>
+        <v>2460.3</v>
       </c>
       <c r="I9" t="n">
         <v>2455.722675605821</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.26</v>
+        <v>-4.7</v>
       </c>
       <c r="L9" t="n">
-        <v>4.75</v>
+        <v>6.51</v>
       </c>
       <c r="M9" t="n">
         <v>1.15</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>4.51</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44827.55208333334</v>
+        <v>44830.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>2568</v>
+        <v>2550</v>
       </c>
       <c r="I10" t="n">
         <v>2554.701950864973</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>24</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>4.38</v>
+        <v>3.65</v>
       </c>
       <c r="L10" t="n">
         <v>0.78</v>
@@ -1011,7 +1130,7 @@
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>2.86</v>
+        <v>4.31</v>
       </c>
       <c r="O10" t="n">
         <v>1.67</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>4.91</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>2637</v>
+        <v>2648.7</v>
       </c>
       <c r="I11" t="n">
         <v>2644.15018807185</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.41</v>
+        <v>-3.87</v>
       </c>
       <c r="L11" t="n">
-        <v>4.5</v>
+        <v>5.88</v>
       </c>
       <c r="M11" t="n">
         <v>2.02</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>5.47</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44879.55208333334</v>
+        <v>44880.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>2686</v>
+        <v>2672.5</v>
       </c>
       <c r="I12" t="n">
         <v>2675.25292758457</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K12" t="n">
-        <v>1.41</v>
+        <v>0.9</v>
       </c>
       <c r="L12" t="n">
         <v>3.98</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>4.94</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44896.55208333334</v>
+        <v>44897.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>2598</v>
+        <v>2684.9</v>
       </c>
       <c r="I13" t="n">
         <v>2621.008908744336</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K13" t="n">
-        <v>2.79</v>
+        <v>-0.46</v>
       </c>
       <c r="L13" t="n">
-        <v>0.91</v>
+        <v>1.37</v>
       </c>
       <c r="M13" t="n">
-        <v>0.57</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>1.48</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
         <v>-2.3</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>5.4</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44910.55208333334</v>
+        <v>44911.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>2969.55</v>
+        <v>2798.6</v>
       </c>
       <c r="I14" t="n">
         <v>2846.134814666332</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K14" t="n">
-        <v>10.6</v>
+        <v>4.23</v>
       </c>
       <c r="L14" t="n">
         <v>3.12</v>
       </c>
       <c r="M14" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="N14" t="n">
-        <v>1.01</v>
+        <v>7.32</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>9.48</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44943.38541666666</v>
+        <v>44943.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>2676.9</v>
+        <v>2726</v>
       </c>
       <c r="I15" t="n">
         <v>2696.016287051995</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>32</v>
+        <v>32.16666666666666</v>
       </c>
       <c r="K15" t="n">
-        <v>4.35</v>
+        <v>2.59</v>
       </c>
       <c r="L15" t="n">
         <v>5.95</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>5.02</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44995.38541666666</v>
+        <v>44995.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>2968.1</v>
+        <v>2948.85</v>
       </c>
       <c r="I16" t="n">
         <v>2963.385506722219</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>51.83333333333334</v>
+        <v>52</v>
       </c>
       <c r="K16" t="n">
-        <v>8.880000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="L16" t="n">
         <v>1.89</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.13</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45016.55208333334</v>
+        <v>45019.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>2879</v>
+        <v>2939.55</v>
       </c>
       <c r="I17" t="n">
         <v>2909.279940829466</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>21</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>2.37</v>
+        <v>0.32</v>
       </c>
       <c r="L17" t="n">
         <v>0.75</v>
@@ -1410,7 +1613,7 @@
         <v>0.99</v>
       </c>
       <c r="N17" t="n">
-        <v>2.32</v>
+        <v>2.71</v>
       </c>
       <c r="O17" t="n">
         <v>-4.29</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>5.42</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45055.55208333334</v>
+        <v>45056.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>3230</v>
+        <v>3191</v>
       </c>
       <c r="I18" t="n">
         <v>3197.152442946907</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K18" t="n">
-        <v>9.880000000000001</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="L18" t="n">
         <v>1.35</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>4.93</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45058.38541666666</v>
+        <v>45058.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>3323.1</v>
+        <v>3382.1</v>
       </c>
       <c r="I19" t="n">
         <v>3335.302003567853</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.14</v>
+        <v>-5.99</v>
       </c>
       <c r="L19" t="n">
-        <v>4.67</v>
+        <v>6.55</v>
       </c>
       <c r="M19" t="n">
         <v>0.24</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>6.07</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45098.38541666666</v>
+        <v>45098.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>3506.5</v>
+        <v>3454</v>
       </c>
       <c r="I20" t="n">
         <v>3473.67291915904</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>39.83333333333334</v>
+        <v>40</v>
       </c>
       <c r="K20" t="n">
-        <v>3.68</v>
+        <v>2.13</v>
       </c>
       <c r="L20" t="n">
         <v>2.55</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>4.1</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45105.38541666666</v>
+        <v>45105.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>3562.9</v>
+        <v>3630.55</v>
       </c>
       <c r="I21" t="n">
         <v>3589.469051426004</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.15</v>
+        <v>-5.11</v>
       </c>
       <c r="L21" t="n">
-        <v>3.18</v>
+        <v>5.29</v>
       </c>
       <c r="M21" t="n">
         <v>0.86</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>5.77</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45180.55208333334</v>
+        <v>45181.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>5150</v>
+        <v>5000</v>
       </c>
       <c r="I22" t="n">
         <v>5080.620223670644</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>75</v>
+        <v>75.83333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>41.85</v>
+        <v>37.72</v>
       </c>
       <c r="L22" t="n">
         <v>3.84</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>6.56</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45187.55208333334</v>
+        <v>45189.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>5137.4</v>
+        <v>5249.45</v>
       </c>
       <c r="I23" t="n">
         <v>5187.826349463229</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.75</v>
+        <v>-4.99</v>
       </c>
       <c r="L23" t="n">
-        <v>4</v>
+        <v>5.46</v>
       </c>
       <c r="M23" t="n">
         <v>0.77</v>
       </c>
       <c r="N23" t="n">
-        <v>2.48</v>
+        <v>3.11</v>
       </c>
       <c r="O23" t="n">
         <v>-3.88</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.89</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45218.55208333334</v>
+        <v>45219.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>5285</v>
+        <v>5202.25</v>
       </c>
       <c r="I24" t="n">
         <v>5232.56356760063</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K24" t="n">
-        <v>0.68</v>
+        <v>-0.9</v>
       </c>
       <c r="L24" t="n">
         <v>3.13</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>8.09</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45245.55208333334</v>
+        <v>45246.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>5130</v>
+        <v>5254</v>
       </c>
       <c r="I25" t="n">
         <v>5176.678103767264</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K25" t="n">
-        <v>1.39</v>
+        <v>-0.99</v>
       </c>
       <c r="L25" t="n">
         <v>3.31</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>5.32</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45281.55208333334</v>
+        <v>45282.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>5605</v>
+        <v>5365</v>
       </c>
       <c r="I26" t="n">
         <v>5461.445220177518</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K26" t="n">
-        <v>6.68</v>
+        <v>2.11</v>
       </c>
       <c r="L26" t="n">
         <v>2.67</v>
@@ -1923,7 +2234,7 @@
         <v>0.03</v>
       </c>
       <c r="N26" t="n">
-        <v>2.71</v>
+        <v>4.34</v>
       </c>
       <c r="O26" t="n">
         <v>2.58</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45337.38541666666</v>
+        <v>45337.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>4402.15</v>
+        <v>4624</v>
       </c>
       <c r="I27" t="n">
         <v>4512.404826882823</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>55</v>
+        <v>55.16666666666666</v>
       </c>
       <c r="K27" t="n">
-        <v>17.95</v>
+        <v>13.81</v>
       </c>
       <c r="L27" t="n">
         <v>5</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>8.07</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45370.38541666666</v>
+        <v>45370.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>4720</v>
+        <v>4678.75</v>
       </c>
       <c r="I28" t="n">
         <v>4694.016005947497</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>32.83333333333334</v>
+        <v>33</v>
       </c>
       <c r="K28" t="n">
-        <v>2.08</v>
+        <v>1.18</v>
       </c>
       <c r="L28" t="n">
         <v>4.84</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>6.48</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45372.38541666666</v>
+        <v>45372.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>4908.5</v>
+        <v>4995</v>
       </c>
       <c r="I29" t="n">
         <v>4981.738406037446</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.833333333333333</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.91</v>
+        <v>-6.76</v>
       </c>
       <c r="L29" t="n">
-        <v>5.4</v>
+        <v>7.41</v>
       </c>
       <c r="M29" t="n">
         <v>1.25</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>7.33</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>6940</v>
+        <v>6493.8</v>
       </c>
       <c r="I30" t="n">
         <v>6547.151747063508</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>74</v>
+        <v>74.83333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>38.94</v>
+        <v>30.01</v>
       </c>
       <c r="L30" t="n">
         <v>2.9</v>
@@ -2151,7 +2510,7 @@
         <v>1.4</v>
       </c>
       <c r="N30" t="n">
-        <v>1.9</v>
+        <v>6.37</v>
       </c>
       <c r="O30" t="n">
         <v>5.38</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>11.3</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45463.55208333334</v>
+        <v>45464.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>6958.25</v>
+        <v>7126.05</v>
       </c>
       <c r="I31" t="n">
         <v>7117.394426390701</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K31" t="n">
-        <v>-7.15</v>
+        <v>-9.74</v>
       </c>
       <c r="L31" t="n">
-        <v>10.49</v>
+        <v>11.11</v>
       </c>
       <c r="M31" t="n">
         <v>1.91</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>6.04</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45470.55208333334</v>
+        <v>45471.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>6998.6</v>
+        <v>6770.1</v>
       </c>
       <c r="I32" t="n">
         <v>6875.935568101208</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.79</v>
+        <v>-5</v>
       </c>
       <c r="L32" t="n">
-        <v>2.51</v>
+        <v>7.16</v>
       </c>
       <c r="M32" t="n">
-        <v>1.34</v>
+        <v>3.29</v>
       </c>
       <c r="N32" t="n">
-        <v>2.66</v>
+        <v>3.77</v>
       </c>
       <c r="O32" t="n">
         <v>1.97</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>6.4</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45502.55208333334</v>
+        <v>45503.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>6585</v>
+        <v>6662</v>
       </c>
       <c r="I33" t="n">
         <v>6615.133424988268</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K33" t="n">
-        <v>2.73</v>
+        <v>1.6</v>
       </c>
       <c r="L33" t="n">
         <v>0.79</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>6.58</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45509.38541666666</v>
+        <v>45509.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>6487.7</v>
+        <v>6440</v>
       </c>
       <c r="I34" t="n">
         <v>6474.575504967032</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.62</v>
+        <v>-3.33</v>
       </c>
       <c r="L34" t="n">
-        <v>3.39</v>
+        <v>3.45</v>
       </c>
       <c r="M34" t="n">
         <v>3.27</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,25 +2834,25 @@
         <v>6.8</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45523.55208333334</v>
+        <v>45524.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>6677.3</v>
+        <v>6785.85</v>
       </c>
       <c r="I35" t="n">
         <v>6733.923129388392</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>-3.68</v>
+        <v>-5.37</v>
       </c>
       <c r="L35" t="n">
-        <v>4.81</v>
+        <v>6.89</v>
       </c>
       <c r="M35" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="N35" t="n">
         <v>4.08</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>6.27</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45553.55208333334</v>
+        <v>45554.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>6660.4</v>
+        <v>6477.05</v>
       </c>
       <c r="I36" t="n">
         <v>6589.515282200588</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K36" t="n">
-        <v>-1.85</v>
+        <v>-4.55</v>
       </c>
       <c r="L36" t="n">
-        <v>4.56</v>
+        <v>4.85</v>
       </c>
       <c r="M36" t="n">
         <v>0.79</v>
       </c>
       <c r="N36" t="n">
-        <v>1.47</v>
+        <v>2.84</v>
       </c>
       <c r="O36" t="n">
         <v>1.26</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>6.34</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45561.55208333334</v>
+        <v>45562.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>6730</v>
+        <v>7070</v>
       </c>
       <c r="I37" t="n">
         <v>6759.659005225099</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.91</v>
+        <v>-9.15</v>
       </c>
       <c r="L37" t="n">
-        <v>4.59</v>
+        <v>9.91</v>
       </c>
       <c r="M37" t="n">
         <v>0.66</v>
       </c>
       <c r="N37" t="n">
-        <v>1.4</v>
+        <v>4.83</v>
       </c>
       <c r="O37" t="n">
         <v>-2.84</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.41</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45582.38541666666</v>
+        <v>45582.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>7210</v>
+        <v>7064</v>
       </c>
       <c r="I38" t="n">
         <v>7075.371774190394</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K38" t="n">
-        <v>1.98</v>
+        <v>-0.08</v>
       </c>
       <c r="L38" t="n">
         <v>4.73</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45601.55208333334</v>
+        <v>45602.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>6610</v>
+        <v>6922</v>
       </c>
       <c r="I39" t="n">
         <v>6778.429599713613</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K39" t="n">
-        <v>6.43</v>
+        <v>2.01</v>
       </c>
       <c r="L39" t="n">
         <v>2.55</v>
       </c>
       <c r="M39" t="n">
-        <v>0.88</v>
+        <v>1.36</v>
       </c>
       <c r="N39" t="n">
-        <v>1.39</v>
+        <v>4.61</v>
       </c>
       <c r="O39" t="n">
         <v>-1.48</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,25 +3179,25 @@
         <v>8.279999999999999</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45608.55208333334</v>
+        <v>45609.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>6494.95</v>
+        <v>6352.3</v>
       </c>
       <c r="I40" t="n">
         <v>6457.808240882364</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K40" t="n">
-        <v>-6.17</v>
+        <v>-8.23</v>
       </c>
       <c r="L40" t="n">
-        <v>6.3</v>
+        <v>9.5</v>
       </c>
       <c r="M40" t="n">
-        <v>-0</v>
+        <v>0.46</v>
       </c>
       <c r="N40" t="n">
         <v>3.07</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,25 +3248,25 @@
         <v>6.98</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>6610.4</v>
+        <v>6785</v>
       </c>
       <c r="I41" t="n">
         <v>6699.381126536634</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.06</v>
+        <v>-6.81</v>
       </c>
       <c r="L41" t="n">
-        <v>4.62</v>
+        <v>7.38</v>
       </c>
       <c r="M41" t="n">
-        <v>0.59</v>
+        <v>3.02</v>
       </c>
       <c r="N41" t="n">
         <v>3.05</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>6.18</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45646.38541666666</v>
+        <v>45646.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>7328.6</v>
+        <v>7208</v>
       </c>
       <c r="I42" t="n">
         <v>7291.673700585866</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K42" t="n">
-        <v>8.01</v>
+        <v>6.23</v>
       </c>
       <c r="L42" t="n">
         <v>1.24</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>5.64</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45673.55208333334</v>
+        <v>45674.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>6665</v>
+        <v>6804.9</v>
       </c>
       <c r="I43" t="n">
         <v>6746.28524839513</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K43" t="n">
-        <v>7.53</v>
+        <v>5.59</v>
       </c>
       <c r="L43" t="n">
         <v>3.22</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>8.6</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45678.55208333334</v>
+        <v>45679.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>6552</v>
+        <v>6272.1</v>
       </c>
       <c r="I44" t="n">
         <v>6363.481311441716</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.72</v>
+        <v>-7.83</v>
       </c>
       <c r="L44" t="n">
-        <v>4.09</v>
+        <v>8.57</v>
       </c>
       <c r="M44" t="n">
         <v>1.1</v>
       </c>
       <c r="N44" t="n">
-        <v>3.65</v>
+        <v>6.52</v>
       </c>
       <c r="O44" t="n">
         <v>1.23</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>10.73</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45708.55208333334</v>
+        <v>45709.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>5760</v>
+        <v>5830.3</v>
       </c>
       <c r="I45" t="n">
         <v>5792.224038780438</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K45" t="n">
-        <v>8.16</v>
+        <v>7.04</v>
       </c>
       <c r="L45" t="n">
         <v>5.32</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>7.65</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45713.55208333334</v>
+        <v>45715.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>5742.65</v>
+        <v>4790.7</v>
       </c>
       <c r="I46" t="n">
         <v>5426.731392286028</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.5</v>
+        <v>-17.83</v>
       </c>
       <c r="L46" t="n">
-        <v>1.99</v>
+        <v>18.51</v>
       </c>
       <c r="M46" t="n">
-        <v>0.6</v>
+        <v>5.97</v>
       </c>
       <c r="N46" t="n">
-        <v>1.41</v>
+        <v>18.59</v>
       </c>
       <c r="O46" t="n">
         <v>0.8</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>18.86</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45734.55208333334</v>
+        <v>45735.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>5175</v>
+        <v>5410.75</v>
       </c>
       <c r="I47" t="n">
         <v>5291.471522740063</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K47" t="n">
-        <v>-8.02</v>
+        <v>-12.94</v>
       </c>
       <c r="L47" t="n">
-        <v>12.72</v>
+        <v>13.33</v>
       </c>
       <c r="M47" t="n">
         <v>2.37</v>
       </c>
       <c r="N47" t="n">
-        <v>4.23</v>
+        <v>4.64</v>
       </c>
       <c r="O47" t="n">
         <v>-18.59</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>9.5</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45735.55208333334</v>
+        <v>45736.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>5415</v>
+        <v>4963</v>
       </c>
       <c r="I48" t="n">
         <v>5057.061080066965</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>0.08</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>4.54</v>
+        <v>9.19</v>
       </c>
       <c r="M48" t="n">
-        <v>-0</v>
+        <v>3.51</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="O48" t="n">
         <v>4.64</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>12.14</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>5079.65</v>
+        <v>5226.5</v>
       </c>
       <c r="I49" t="n">
         <v>5177.766900163723</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.35</v>
+        <v>-5.31</v>
       </c>
       <c r="L49" t="n">
         <v>6.08</v>
@@ -3234,7 +3821,7 @@
         <v>2.02</v>
       </c>
       <c r="N49" t="n">
-        <v>2.43</v>
+        <v>3.39</v>
       </c>
       <c r="O49" t="n">
         <v>-5.78</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>8.720000000000001</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45826.55208333334</v>
+        <v>45827.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>5984.5</v>
+        <v>5810</v>
       </c>
       <c r="I50" t="n">
         <v>5947.142353841678</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>64.16666666666667</v>
+        <v>65</v>
       </c>
       <c r="K50" t="n">
-        <v>14.5</v>
+        <v>11.16</v>
       </c>
       <c r="L50" t="n">
         <v>1.96</v>
@@ -3291,7 +3890,7 @@
         <v>4.84</v>
       </c>
       <c r="N50" t="n">
-        <v>2.41</v>
+        <v>2.82</v>
       </c>
       <c r="O50" t="n">
         <v>3.39</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>7.7</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45828.55208333334</v>
+        <v>45831.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>5982</v>
+        <v>6296</v>
       </c>
       <c r="I51" t="n">
         <v>6160.01835247781</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.96</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>3.54</v>
+        <v>9.02</v>
       </c>
       <c r="M51" t="n">
-        <v>0.15</v>
+        <v>0.31</v>
       </c>
       <c r="N51" t="n">
-        <v>2.85</v>
+        <v>4.46</v>
       </c>
       <c r="O51" t="n">
         <v>-2.82</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>9.1</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45925.38541666666</v>
+        <v>45925.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>7471</v>
+        <v>7385</v>
       </c>
       <c r="I52" t="n">
         <v>7389.005920139804</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>94</v>
+        <v>94.16666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>18.66</v>
+        <v>17.3</v>
       </c>
       <c r="L52" t="n">
         <v>5.1</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>133</v>
+        <v>134</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>4</v>
+      </c>
+      <c r="U52" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>4.91</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45936.38541666666</v>
+        <v>45936.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>7486.5</v>
+        <v>7629</v>
       </c>
       <c r="I53" t="n">
         <v>7577.210666880597</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>10.83333333333333</v>
+        <v>11</v>
       </c>
       <c r="K53" t="n">
-        <v>-1.37</v>
+        <v>-3.3</v>
       </c>
       <c r="L53" t="n">
-        <v>1.83</v>
+        <v>3.51</v>
       </c>
       <c r="M53" t="n">
         <v>0.74</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>5.03</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45947.38541666666</v>
+        <v>45947.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>7587</v>
+        <v>7450</v>
       </c>
       <c r="I54" t="n">
         <v>7451.810127324533</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>10.83333333333333</v>
+        <v>11</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.55</v>
+        <v>-2.35</v>
       </c>
       <c r="L54" t="n">
-        <v>2.08</v>
+        <v>5.11</v>
       </c>
       <c r="M54" t="n">
         <v>0.36</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>5.11</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45959.55208333334</v>
+        <v>45960.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>7729.5</v>
+        <v>7842.5</v>
       </c>
       <c r="I55" t="n">
         <v>7830.820153955199</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K55" t="n">
-        <v>-3.75</v>
+        <v>-5.27</v>
       </c>
       <c r="L55" t="n">
-        <v>4.13</v>
+        <v>5.33</v>
       </c>
       <c r="M55" t="n">
         <v>1.07</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>5.83</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45982.55208333334</v>
+        <v>45985.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>7522</v>
+        <v>7459.5</v>
       </c>
       <c r="I56" t="n">
         <v>7469.556247307972</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K56" t="n">
-        <v>-4.09</v>
+        <v>-4.88</v>
       </c>
       <c r="L56" t="n">
-        <v>4.99</v>
+        <v>5.32</v>
       </c>
       <c r="M56" t="n">
         <v>0.31</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>3.81</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46010.38541666666</v>
+        <v>46010.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>7319.5</v>
+        <v>7435</v>
       </c>
       <c r="I57" t="n">
         <v>7351.245770582451</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K57" t="n">
-        <v>1.88</v>
+        <v>0.33</v>
       </c>
       <c r="L57" t="n">
         <v>1.46</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.59</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46034.55208333334</v>
+        <v>46035.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>7624.5</v>
+        <v>7486.5</v>
       </c>
       <c r="I58" t="n">
         <v>7559.403332615655</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>24</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K58" t="n">
-        <v>2.55</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L58" t="n">
         <v>1.56</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>5.95</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>7055</v>
+        <v>7469</v>
       </c>
       <c r="I59" t="n">
         <v>7207.900158812276</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K59" t="n">
-        <v>5.76</v>
+        <v>0.23</v>
       </c>
       <c r="L59" t="n">
-        <v>2.36</v>
+        <v>2.85</v>
       </c>
       <c r="M59" t="n">
-        <v>1.84</v>
+        <v>4.89</v>
       </c>
       <c r="N59" t="n">
-        <v>5.14</v>
+        <v>6.38</v>
       </c>
       <c r="O59" t="n">
         <v>-1.4</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>7.39</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46087.55208333334</v>
+        <v>46090.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>8562</v>
+        <v>8238</v>
       </c>
       <c r="I60" t="n">
         <v>8243.831494155902</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K60" t="n">
-        <v>14.63</v>
+        <v>10.3</v>
       </c>
       <c r="L60" t="n">
         <v>1.46</v>
@@ -3861,7 +4580,7 @@
         <v>2.4</v>
       </c>
       <c r="N60" t="n">
-        <v>3.17</v>
+        <v>3.82</v>
       </c>
       <c r="O60" t="n">
         <v>6.38</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>7.36</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>7230</v>
+        <v>7589.5</v>
       </c>
       <c r="I61" t="n">
         <v>7347.056982655515</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K61" t="n">
-        <v>12.24</v>
+        <v>7.87</v>
       </c>
       <c r="L61" t="n">
         <v>2.63</v>
@@ -3918,7 +4649,7 @@
         <v>4.66</v>
       </c>
       <c r="N61" t="n">
-        <v>3.94</v>
+        <v>5.17</v>
       </c>
       <c r="O61" t="n">
         <v>-3.82</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46197.55208333334</v>
+        <v>46198.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>9700</v>
+        <v>9580</v>
       </c>
       <c r="I62" t="n">
         <v>9609.41334903895</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>77.16666666666667</v>
+        <v>78</v>
       </c>
       <c r="K62" t="n">
-        <v>27.81</v>
+        <v>26.23</v>
       </c>
       <c r="L62" t="n">
         <v>2.03</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>5.34</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46240.38541666666</v>
+        <v>46240.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>9240</v>
+        <v>9290</v>
       </c>
       <c r="I63" t="n">
         <v>9273.793082868719</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>42</v>
+        <v>42.16666666666666</v>
       </c>
       <c r="K63" t="n">
-        <v>3.55</v>
+        <v>3.03</v>
       </c>
       <c r="L63" t="n">
         <v>4.47</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>3.78</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46254.55208333334</v>
+        <v>46255.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>9119</v>
+        <v>8998.5</v>
       </c>
       <c r="I64" t="n">
         <v>9034.834260778207</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K64" t="n">
-        <v>-1.84</v>
+        <v>-3.14</v>
       </c>
       <c r="L64" t="n">
         <v>3.51</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>4.78</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46304.55208333334</v>
+        <v>46307.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>8240</v>
+        <v>8441.5</v>
       </c>
       <c r="I65" t="n">
         <v>8311.546373852221</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K65" t="n">
-        <v>8.43</v>
+        <v>6.19</v>
       </c>
       <c r="L65" t="n">
         <v>2.35</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>5.74</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46314.38541666666</v>
+        <v>46314.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>8065.5</v>
+        <v>8000</v>
       </c>
       <c r="I66" t="n">
         <v>8014.545109433595</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K66" t="n">
-        <v>-4.45</v>
+        <v>-5.23</v>
       </c>
       <c r="L66" t="n">
         <v>7.1</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4263,6 +5066,14 @@
       <c r="Q67" t="n">
         <v>13</v>
       </c>
+      <c r="R67" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6365,7 +7176,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.9</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="6">
@@ -6375,7 +7186,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.2</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="7">
@@ -6385,7 +7196,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>94.2</v>
       </c>
     </row>
     <row r="8">
@@ -6395,7 +7206,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -6405,7 +7216,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -6415,7 +7226,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54.2</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="11">
@@ -6455,7 +7266,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.86</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="15">
@@ -6465,7 +7276,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.33</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="16">
@@ -6475,7 +7286,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.3</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="17">
@@ -6485,7 +7296,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>41.85</v>
+        <v>37.72</v>
       </c>
     </row>
     <row r="18">
@@ -6495,7 +7306,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>58.5</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="19">
@@ -6505,7 +7316,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.86</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="20">
@@ -6515,7 +7326,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.51</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="21">
@@ -6525,7 +7336,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12.72</v>
+        <v>18.51</v>
       </c>
     </row>
     <row r="22">
@@ -6535,7 +7346,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
@@ -6545,7 +7356,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -6555,7 +7366,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="25">
@@ -6565,7 +7376,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.84</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="26">
@@ -6575,7 +7386,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.08</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="27">
@@ -6585,7 +7396,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.85</v>
+        <v>18.59</v>
       </c>
     </row>
     <row r="28">
@@ -6595,7 +7406,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
